--- a/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
+++ b/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
+++ b/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>06.06.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 85mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktwyne metabolicznie węzły chłonne przedziałów III i IV obustronnie wielkości do 10mm, SUV max do 3,7 Asymetryczne pobudzenie metaboliczne w topografii migdałka gardłowego lewego, SUV max do 5,8- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: przytchawicze głównie po stronie prawej, śródpiersiowe, przy łuku aorty, podostrogowe, przyprzełykowe wielkości do 32mm wg PET, SUV max do 9,0. Pobudzenie metaboliczne w masach miękkotkankowych grubości do 20mm w śródpiersiu przednim w topografii grasicy SUV max do 4,0 [pomiar na Im 125] Zmiana guzkowo- włóknista w segmencie 3 płuca prawego wielkości 10mm wg PET, SUV max 3,2.   Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Przyśródpiersiowo w płacie górnym i środkowym płuca prawego widoczne pogrubienia przegrodowe.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii prawych przydatków wielkości 19mm wg PET, SUV max 7,7- do pilnej weryfikacji ginekologicznej.  Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s.6 brzeżnie- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona wielkości 119x36x75mm.  Układ kostny: Pobudzenie metaboliczne w całym układzie kostnym. Zwiększony metabolizm FDG w topografii linii cięcia rękojeści mostka - stan po sternotomii, SUV max 4,6.  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej powyżej poziomu przeponu. Wskazana pilna kontrola ginekologiczna.  Zmiana guzkowo- włóknista w segmencie 3 płuca prawego - do kontroli/weryfikacji.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>23.08.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Stan po ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 96mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu w topografii grasicy pasmotawe wzmożenie cieniowania tkanki tłuszczowej grubości do  20mm- do weryfikacji.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w całym układzie kostnym- związane ze stosowanym leczeniem?  Wartości referencyjne: MBPS SUVmax do 2,1 Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>08.11.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Choroba Hodgkina (stwardnienie guzkowe). Ocena remisji po zakończeniu chemioterapii przed kwalifikacją do IFRT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do  20mm - do oceny w badaniu TK KLP. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>25.04.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Choroba Hodgkina (stwardnienie guzkowe). Ocena remisji po zakończeniu chemioterapii 3 miesiące po IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Dość symetryczna aktywność metaboliczna w topografii trąbek słuchowych oraz strukturach pierścienia Waldeyera, SUV max do 6,6 - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do 17mm. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.  Brzuch i miednica: Aktywność metaboliczna w obrębie torbieli w topografii przydatków lewych, SUV max 9,7 - czynnościowa? - do ew. oceny ginekologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>9.699999999999999</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
+++ b/pacjenci/AGNIESZKA STANKIEWICZ.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 85mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktwyne metabolicznie węzły chłonne przedziałów III i IV obustronnie wielkości do 10mm, SUV max do 3,7 Asymetryczne pobudzenie metaboliczne w topografii migdałka gardłowego lewego, SUV max do 5,8- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: przytchawicze głównie po stronie prawej, śródpiersiowe, przy łuku aorty, podostrogowe, przyprzełykowe wielkości do 32mm wg PET, SUV max do 9,0. Pobudzenie metaboliczne w masach miękkotkankowych grubości do 20mm w śródpiersiu przednim w topografii grasicy SUV max do 4,0 [pomiar na Im 125] Zmiana guzkowo- włóknista w segmencie 3 płuca prawego wielkości 10mm wg PET, SUV max 3,2.   Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Przyśródpiersiowo w płacie górnym i środkowym płuca prawego widoczne pogrubienia przegrodowe.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii prawych przydatków wielkości 19mm wg PET, SUV max 7,7- do pilnej weryfikacji ginekologicznej.  Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s.6 brzeżnie- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona wielkości 119x36x75mm.  Układ kostny: Pobudzenie metaboliczne w całym układzie kostnym. Zwiększony metabolizm FDG w topografii linii cięcia rękojeści mostka - stan po sternotomii, SUV max 4,6.  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktwyne metabolicznie węzły chłonne przedziałów III i IV obustronnie wielkości do 10mm, SUV max do 3,7 Asymetryczne pobudzenie metaboliczne w topografii migdałka gardłowego lewego, SUV max do 5,8- do kontroli.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: przytchawicze głównie po stronie prawej, śródpiersiowe, przy łuku aorty, podostrogowe, przyprzełykowe wielkości do 32mm wg PET, SUV max do 9,0. Pobudzenie metaboliczne w masach miękkotkankowych grubości do 20mm w śródpiersiu przednim w topografii grasicy SUV max do 4,0 [pomiar na Im 125] Zmiana guzkowo- włóknista w segmencie 3 płuca prawego wielkości 10mm wg PET, SUV max 3,2.   Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Przyśródpiersiowo w płacie górnym i środkowym płuca prawego widoczne pogrubienia przegrodowe.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w topografii prawych przydatków wielkości 19mm wg PET, SUV max 7,7- do pilnej weryfikacji ginekologicznej.  Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s.6 brzeżnie- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona wielkości 119x36x75mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w całym układzie kostnym. Zwiększony metabolizm FDG w topografii linii cięcia rękojeści mostka - stan po sternotomii, SUV max 4,6.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej powyżej poziomu przeponu. Wskazana pilna kontrola ginekologiczna.  Zmiana guzkowo- włóknista w segmencie 3 płuca prawego - do kontroli/weryfikacji.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 96mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu w topografii grasicy pasmotawe wzmożenie cieniowania tkanki tłuszczowej grubości do  20mm- do weryfikacji.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w całym układzie kostnym- związane ze stosowanym leczeniem?  Wartości referencyjne: MBPS SUVmax do 2,1 Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu w topografii grasicy pasmotawe wzmożenie cieniowania tkanki tłuszczowej grubości do  20mm- do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w całym układzie kostnym- związane ze stosowanym leczeniem?</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.2</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do  20mm - do oceny w badaniu TK KLP. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do  20mm - do oceny w badaniu TK KLP. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w topografii pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Dość symetryczna aktywność metaboliczna w topografii trąbek słuchowych oraz strukturach pierścienia Waldeyera, SUV max do 6,6 - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do 17mm. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.  Brzuch i miednica: Aktywność metaboliczna w obrębie torbieli w topografii przydatków lewych, SUV max 9,7 - czynnościowa? - do ew. oceny ginekologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dość symetryczna aktywność metaboliczna w topografii trąbek słuchowych oraz strukturach pierścienia Waldeyera, SUV max do 6,6 - do oceny klinicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste i niewielkie nawarstwienia opłucnowe w szczycie płuca lewego. W śródpiersiu przednim w topografii grasicy pasmowate wzmożenie cieniowania tkanki tłuszczowej o grubości do 17mm. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 4 i 5 płuca lewego oraz obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w obrębie torbieli w topografii przydatków lewych, SUV max 9,7 - czynnościowa? - do ew. oceny ginekologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowe kręgosłupa. Odcinkowe zwapnienie wewnątrzkanałowo, w topografii więzadła podłużnego tylnego, na poziomie C7-Th1. Ok. 5mm wyspa kostna w przednio-prawobocznej części trzonu Th4. Dyskopatia L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych w dolnym segmencie kręgosłupa lędźwiowego.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>9.699999999999999</v>
       </c>
     </row>
